--- a/course_data/shop_data.xlsx
+++ b/course_data/shop_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaoya_chang/Documents/Playground/Data_to_Decision_with_SQL_Python/course_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{68617E88-AEF9-D644-AEBD-FB63FF152487}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C7D1AE6-1F82-A348-8C62-269DE00CE250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="700" yWindow="820" windowWidth="26340" windowHeight="15760" activeTab="2" xr2:uid="{D6797BD4-1FA8-004F-8F87-822C28CD1625}"/>
+    <workbookView xWindow="-29160" yWindow="980" windowWidth="26340" windowHeight="15760" activeTab="3" xr2:uid="{D6797BD4-1FA8-004F-8F87-822C28CD1625}"/>
   </bookViews>
   <sheets>
     <sheet name="shop_orders" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="58">
   <si>
     <t>order_id</t>
   </si>
@@ -195,6 +195,9 @@
   </si>
   <si>
     <t>Water Bottle</t>
+  </si>
+  <si>
+    <t>age</t>
   </si>
 </sst>
 </file>
@@ -763,17 +766,17 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
+        <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{50C9C8D7-DC8E-25FD-FAD6-317328DE0156}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C51C4F8A-7FB2-EA53-AD03-DF2A69718DD2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -783,6 +786,7 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect r="17157"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -790,7 +794,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="7772400" cy="5181600"/>
+          <a:ext cx="6438900" cy="5829300"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1843,7 +1847,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -1856,7 +1860,9 @@
       <c r="C1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="1"/>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
@@ -1868,7 +1874,9 @@
       <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="2">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -1880,7 +1888,9 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="2">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -1892,7 +1902,9 @@
       <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="2"/>
+      <c r="D4" s="2">
+        <v>41</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -1904,7 +1916,9 @@
       <c r="C5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="2"/>
+      <c r="D5" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -1916,7 +1930,9 @@
       <c r="C6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="2">
+        <v>37</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -1928,7 +1944,9 @@
       <c r="C7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -1940,7 +1958,9 @@
       <c r="C8" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
@@ -1952,7 +1972,9 @@
       <c r="C9" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -1964,7 +1986,9 @@
       <c r="C10" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2">
+        <v>52</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -1976,7 +2000,9 @@
       <c r="C11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="2">
+        <v>33</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -1988,7 +2014,9 @@
       <c r="C12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="2">
+        <v>44</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -2000,7 +2028,9 @@
       <c r="C13" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="2">
+        <v>27</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -2012,7 +2042,9 @@
       <c r="C14" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2">
+        <v>39</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -2024,7 +2056,9 @@
       <c r="C15" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2">
+        <v>48</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -2036,7 +2070,9 @@
       <c r="C16" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="2">
+        <v>36</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
@@ -2048,7 +2084,9 @@
       <c r="C17" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" s="2">
+        <v>23</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
@@ -2060,7 +2098,9 @@
       <c r="C18" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" s="2">
+        <v>55</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
@@ -2072,7 +2112,9 @@
       <c r="C19" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="2">
+        <v>42</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -2084,7 +2126,9 @@
       <c r="C20" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" s="2">
+        <v>30</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -2096,187 +2140,9 @@
       <c r="C21" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1"/>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="1"/>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1"/>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="1"/>
-      <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="1"/>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="1"/>
-      <c r="B29" s="2"/>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="1"/>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="1"/>
-      <c r="B31" s="2"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="1"/>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="1"/>
-      <c r="B35" s="2"/>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="1"/>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="1"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="1"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="1"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="1"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="1"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="1"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="1"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="2"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="1"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="1"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="1"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="1"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="1"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="1"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="1"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="1"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="D21" s="2">
+        <v>26</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2285,7 +2151,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
@@ -2581,6 +2447,186 @@
       <c r="D21" s="2">
         <v>33</v>
       </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="1"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="1"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="1"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="1"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="1"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="1"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="1"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="1"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="1"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="1"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="1"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="1"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="1"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="1"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="1"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="1"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+      <c r="D51" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
